--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -73,13 +73,13 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>16.16 seconds</t>
+    <t>16.75 seconds</t>
   </si>
   <si>
     <t>Timestamp</t>
   </si>
   <si>
-    <t>23/6/2026, 3:34:25 pm</t>
+    <t>23/7/2026, 2:54:00 pm</t>
   </si>
 </sst>
 </file>
